--- a/Data/Lambayeque/noticias_lambayeque_20260921_20260928.xlsx
+++ b/Data/Lambayeque/noticias_lambayeque_20260921_20260928.xlsx
@@ -470,10 +470,99 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Apurímac: trasladarán puente modular para restablecer el tránsito tras colapsar estructura</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>El titular del MTC explicó que, a través de Provías Descentralizado, se trasladará un puente modular hasta el lugar de la emergencia.
+Para ello, los equipos técnicos evalúan la desinstalación de una estructura que se encuentra aproximadamente a 51 kilómetros del punto donde será instalada.
+“Vamos a disponer de un puente modular con la finalidad de trasladarlo hasta ese punto y poder restablecer el tránsito normal en esta zona”, manifestó a su llegada a Cusco donde luego abordó una aeronave para trasladarse a Apurímac.
+El ministro precisó que previamente se realizará una evaluación técnica para determinar las condiciones de instalación de la estructura y garantizar su adecuado funcionamiento.
+MTC apoyará pese a que puente corresponde al Gore Apurímac El ministro Tangherlini explicó que el puente colapsado se encuentra bajo la jurisdicción del Gobierno Regional de Apurímac.
+Sin embargo, ante la necesidad de recuperar rápidamente la transitabilidad, el MTC decidió intervenir con recursos del sector.
+Para formalizar esta intervención, anunció que se suscribirá un convenio con el Gobierno Regional de Apurímac, con el objetivo de que el Ejecutivo pueda ejecutar las acciones correspondientes sin interferir en las competencias de la autoridad regional.
+“Es importante indicar que este puente se encuentra bajo la jurisdicción del gobierno regional; sin embargo, nosotros hemos decidido dar una acción rápida y brindar nuestro apoyo al gobierno regional”, afirmó.
+El ministro se trasladó posteriormente hacia Apurímac junto con una comitiva para supervisar la situación generada por el colapso de la estructura.
+Dos camiones pesados habrían provocado el colapso Respecto a las causas del incidente, el ministro informó que, según la información recibida por el MTC, el colapso se produjo el sábado cuando dos camiones de carga pesada cruzaron el puente sin respetar las señalizaciones existentes.
+Al tratarse de una estructura bajo jurisdicción regional, indicó que la evaluación y las acciones relacionadas con su condición corresponden inicialmente a dicha autoridad.
+Consultado sobre la existencia de otros puentes que pudieran encontrarse en condiciones críticas, el ministro señaló que el MTC cuenta con una relación de estructuras que requieren intervención y que se vienen ejecutando acciones de mantenimiento y trabajos destinados a garantizar su seguridad.
+Mencionó que existen puentes identificados como críticos en diferentes regiones, entre ellas Piura, Lambayeque, Cusco, Apurímac y Puno.
+MTC prepara puentes y maquinaria ante El Niño El titular del sector informó también que el Gobierno ha identificado puntos críticos de la infraestructura vial nacional ante los posibles efectos del fenómeno El Niño.
+En ese contexto, Provías Nacional y Provías Descentralizado están disponiendo maquinaria en lugares considerados vulnerables, con el propósito de responder rápidamente ante interrupciones del tránsito.
+Asimismo, indicó que se están movilizando puentes modulares hacia diferentes puntos del país, de modo que puedan encontrarse próximos a las zonas donde eventualmente se produzcan emergencias y puedan ser instalados con mayor rapidez.
+“Estamos movilizando puentes en diferentes lugares del país para tenerlos en zonas cercanas y poder instalarlos a la medida que se necesite por las urgencias y las emergencias del fenómeno del Niño”, explicó.
+Esta estrategia busca reducir los tiempos de respuesta ante eventuales daños en carreteras y puentes ocasionados por lluvias intensas, desbordes de ríos, activación de quebradas u otros eventos asociados a la temporada de lluvias.
+MTC asegura continuidad del proyecto del aeropuerto de Chinchero Durante su visita a Cusco, el ministro también se pronunció sobre la situación del Aeropuerto Internacional de Chinchero, proyecto que se ejecuta bajo la modalidad de gobierno a gobierno.
+La autoridad aseguró que el proyecto continúa y su ejecución está garantizada, pese a los aspectos presupuestales que se encuentran en proceso de solución.
+Precisó que actualmente existen tres componentes que presentan avances: la torre de control, el lado tierra y la construcción del terminal, además del cerco perimétrico, de acuerdo con su declaración.
+“Estamos también buscando soluciones a algunos temas presupuestales que se han presentado en el camino, pero durante esta gestión lo que se está buscando es solucionar y destrabar estos aspectos”, sostuvo.
+El ministro destacó que el objetivo es continuar con la ejecución de la infraestructura, a la que calificó como importante para el desarrollo turístico, social y económico de Cusco.
+Conectividad será reforzada para visita del papa León XIV Otro de los temas abordados fue la próxima visita del papa León XIV al Perú, respecto de la cual el ministro señaló que el Ejecutivo considera que tendrá relevancia no solo religiosa y cultural, sino también económica.
+Según explicó, la llegada del pontífice podría generar movimiento en actividades vinculadas con el turismo, comercio y restaurantes, además de contribuir a promocionar diferentes destinos turísticos del país.
+En materia de transporte y conectividad, aseguró que se viene desarrollando un trabajo planificado para garantizar el desplazamiento en las regiones vinculadas con la visita papal, entre ellas Cusco y Madre de Dios, según mencionó.
+“Al respecto, sobre todo el tema de conectividad, eso está asegurado”, afirmó.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-apurimac-trasladaran-puente-modular-para-restablecer-transito-tras-colapsar-estructura-1093687.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chiclayo: Indecopi activa alerta ante masiva llegada de visitantes por arribo de León XIV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>La iniciativa busca prevenir que los visitantes y usuarios sean afectados por problemas en la contratación de servicios durante los días de la visita papal.
+Lea también: León XIV: todo sobre su visita a Chiclayo y la intensa agenda que realizará en noviembre Según explicó Vanessa Huaccha Vidaurre, jefa de la Oficina Regional del Indecopi de Lambayeque, el documento reúne información sobre los derechos de los consumidores y las acciones que pueden adoptar ante eventuales incumplimientos.
+Uno de los principales focos de atención es el transporte aéreo.
+La funcionaria informó que, a agosto de 2026, este sector acumula más de 3,000 reclamos a nivel nacional, por lo que recomendó a los pasajeros conocer sus derechos frente a situaciones como sobreventa de pasajes, cancelaciones y otras contingencias.
+Lea también: Cocinera que alimentó al papa León XIV espera volver a prepararle sus platos favoritos Indecopi también exhortó a los consumidores a verificar antes de contratar las condiciones, precios y características del servicio, además de conservar boletos, comprobantes, reservas, contratos y cualquier documento que pueda servir como sustento ante un eventual reclamo.
+La recomendación alcanza también a quienes contraten hoteles, restaurantes, transporte terrestre y servicios turísticos, especialmente en las ciudades que recibirán al pontífice y a una importante cantidad de visitantes.
+La representante de Indecopi recordó que, si el proveedor no brinda una solución ante un reclamo, los consumidores pueden recurrir a los mecanismos de atención de la institución.
+La entidad cuenta, además, con una plataforma virtual para presentar reclamos y adjuntar documentos de manera remota.
+En Lambayeque, la oficina regional atiende diariamente a alrededor de 80 personas, mientras que los canales virtuales permanecen disponibles las 24 horas.
+La guía de recomendaciones puede ser ubicada gratuitamente mediante los buscadores de internet con términos relacionados con la visita del papa León XIV y recomendaciones de consumo.
+La presentación se produce mientras el Perú intensifica los preparativos para recibir al pontífice entre el 11 y el 16 de noviembre de 2026.
+La visita se proyecta además como un importante movimiento turístico y económico para las regiones incluidas en su recorrido.
+Más en Andina:</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-chiclayo-indecopi-activa-alerta-ante-masiva-llegada-visitantes-arribo-leon-xiv-1093668.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Otro periodo de nieve, granizo y lluvia pronostica el Senamhi en la sierra centro y sur</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>El granizo caería en zonas por encima de los 2800 m s.
 n.
@@ -500,27 +589,27 @@
 Más en Andina: La selva peruana registrará lluvias y un descenso de las temperaturas diurnas y nocturnas debido al ingreso del décimo primer friaje del año, que afectará la selva peruana desde la tarde del miércoles 30 de septiembre hasta el viernes 2 de octubre, anunció el Senamhi.… pic.twitter.com/8jI3RMcfFm — Agencia Andina (@Agencia_Andina) September 27, 2026</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-otro-periodo-nieve-granizo-y-lluvia-pronostica-senamhi-la-sierra-centro-y-sur-1093630.aspx</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>46293</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>"Nos preparamos para El Niño con una gestión preventiva de cartera" [Entrevista]</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Para conocer más detalles sobre este sector de las microfinanzas el Diario El Peruano entrevistó al presidente de la Federación de Cajas Municipales de Ahorro y Crédito ( FEPCMAC ), Luis Vergara Sahuaraura.
 - El fenómeno El Niño está aquí ¿cómo se han preparado las Cajas para afrontar este fenómeno que se prolongaría hasta el próximo año? Las Cajas Municipales se han venido preparando mediante una gestión preventiva de cartera y continuidad operativa.
@@ -559,112 +648,46 @@
 ?? https://t.co/tvJEpbnPKh ??Sonia… pic.twitter.com/Wl8aertZq6 — Agencia Andina (@Agencia_Andina) September 23, 2026</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-nos-preparamos-para-nino-una-gestion-preventiva-cartera-entrevista-1093626.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Produce acelera acciones para reactivar la pesca artesanal en San José, Lambayeque</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>El titular de la cartera explicó que las decisiones sobre el manejo pesquero requieren el respaldo científico del Instituto del Mar del Perú (Imarpe) , por lo que destacó el fortalecimiento de su equipo científico y el trabajo que se realiza para contar con información actualizada sobre las condiciones del mar y los recursos disponibles.
-“Yo no he venido acá a quejarme, he venido a ser parte de la solución, junto con ustedes.
-El sistema de cuotas (de pesca) es una herramienta, pero por sí sola no es suficiente.
-Lo que tenga que decidirse, tiene que decidirse ya.
-No puede esperar”, señaló Requejo.
-Lee también: [ Presidenta anuncia que recibió invitación de Nayib Bukele para visitar El Salvador ] En ese marco, informó que se encuentra en desarrollo un crucero de investigación en el que participa parte de la flota, el cual permitirá obtener información sobre especies como anchoveta, bonito y calamar.
-Agregó que se busca contar con los resultados lo antes posible, a fin de evaluar nuevas medidas.
-Finalmente, Requejo reafirmó su compromiso de trabajar junto a los pescadores para encontrar alternativas que permitan mantener la actividad hasta fin de año y avanzar hacia un escenario de mayor ordenamiento para el próximo periodo.
-"Esta visita se dio en cumplimiento del compromiso de la presidenta de la República, Keiko Fujimori, y de la política del Gobierno de trabajar directamente en los territorios, escuchando las necesidades de los sectores productivos y buscando soluciones directamente con los actores", destacó Produce.
-Posteriormente, el ministro participó en la inauguración del Gran Mercado de Abastos junto con la mandataria, tras lo cual continuó con el trabajo territorial y el diálogo directo con el sector para abordar la agenda pendiente de la pesca artesanal.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-produce-acelera-acciones-para-reactivar-pesca-artesanal-san-jose-lambayeque-1093635.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Presidenta anuncia que recibió invitación de Nayib Bukele para visitar El Salvador</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Así lo señaló durante una transmisión en vivo en sus redes sociales, en la cual también participó el canciller Carlos Espá , quien confirmó la noticia.
-La jefa de Estado calificó este anuncio como "una gran noticia" e indicó que por el momento no podía dar más detalles de la invitación que le ha extendido el mandatario salvadoreño.
-Por su parte, el ministro de Relaciones Exteriores, expresó su emoción y resaltó que el presidente Bukele "tiene muchas lecciones aprendidas para compartir" con nuestro país.
-"Estoy seguro que esas lecciones aprendidas también van a servir para que nosotros podamos responder efectivamente a las justas demandas del pueblo peruano por mayor seguridad ciudadana ", agregó Espá y Garcés Alvear.
-Lee también: [ Presidenta: “Esperamos las facultades legislativas, pero nosotros seguimos avanzando" ] Invitación a la reina Máxima En otro momento, mientras hacía un recuento de sus actividades en Nueva York, a donde viajó con el canciller y otros tres ministros para participar en el periodo de sesiones de la Asamblea de las Naciones Unidas, mencionó su reunión con la reina Máxima de los Países Bajos, a quien invitó a visitar nuestro país.
-Precisó que la reina consorte —nacida en Argentina— dirige en la ONU un programa que promueve la inclusión financiera de las mujeres y que el Perú está adscrito a esta iniciativa.
-"Fue un gusto poder saludarla y también ratificarle el compromiso de nuestro país para poder, a través de los programas de microcrédito, ayudar a diferentes mujeres emprendedoras.
-Esto nos permite luego que estas mamás puedan darle mejor calidad de vida a sus hijos, a disminuir las cifras de pobreza, así que hemos invitado a la reina Máxima para que el próximo año ella pueda venir a nuestro país " , indicó la jefa de Estado.
-Interés de inversionistas En otro momento de la transmisión, la presidenta Fujimori resaltó que en diferentes actividades en las que participó durante su viaje a Estados Unidos pudo hablar del Perú y de sus auspiciosas cifras macroeconómicas, lo que ha generado el interés de inversionistas.
-"Les hemos hablado del Banco Central de Reserva, de la Constitución Política de nuestro país, de las reglas claras.
-Así que yo creo que han sido muy buenas reuniones ", indicó.
-Destacó también la importancia de las micro y pequeñas empresas para mover la economía del Perú.
-En esa línea, resaltó que su Gobierno los ayudará a evitar trabas burocráticas que puedan frenar su dinamismo.
-Relanzamiento de Alianza del Pacífico Por su parte, el canciller Espá mencionó que, en el marco del viaje a Nueva York, sostuvo diferentes reuniones bilaterales y entre ellas destacó el encuentro con su homólogo de México, Roberto Velazco , en donde se abordó la transmisión de la presidencia pro tempore de la Alianza del Pacífico al Perú el próximo año.
-" Va a ser el relanzamiento de la Alianza del Pacífico, que lo que busca es no solamente la integración comercial y económica, sino la integración financiera de las bolsas de valores de los países que integran la Alianza del Pacífico.
-Va a ser muy importante y veo con mucho optimismo, esperanza también, lo fructífera que va a ser su encuentro con la presidenta (Claudia) Sheinbaum de México ", expresó a la jefa de Estado.
-Relación con Venezuela y Marruecos El titular de Relaciones Exteriores resaltó también su reunión con el canciller de Venezuela, Félix Plasencia , tras haberse normalizado las relaciones del Perú con dicho país a nivel consular, en beneficio de los connacionales que se encuentran allá.
-Indicó, además, que el Perú ve con mucha atención la evolución de su situación política e hizo votos para el restablecimiento de la democracia en Venezuela.
-"En esa medida, por supuesto, nosotros vamos a ser de los primeros países que vamos a establecer relaciones diplomáticas (con Venezuela) " , sostuvo Espá.
-De igual modo, destacó la reunión bilateral con su homólogo de Marruecos, Nasser Bourita, con quien emitió un comunicado conjunto en donde el Perú respalda su posición sobre el Sahara Occidental y se relanzan las relaciones comerciales con el país africano, lo que consideró muy auspicioso.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-presidenta-anuncia-recibio-invitacion-nayib-bukele-para-visitar-salvador-1093633.aspx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Keiko Fujimori sobre facultades legislativas: “Estamos demostrando paciencia porque llevan semanas”</t>
+          <t>Sunat inició inscripción para el sorteo de comprobantes de pago: regístrate en este link</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La presidenta Keiko Fujimori cuestionó este domingo la demora del Congreso en el trámite de las facultades legislativas solicitadas por el Ejecutivo y aseguró que su gobierno está mostrando “paciencia” mientras espera que el Parlamento se pronuncie. “Estamos esperando facultades por parte del Congreso, estamos demostrando paciencia porque llevan semanas”, declaró Fujimori durante una actividad en la ciudad de Reque, en Lambayeque, donde participó en la inauguración del mercado modelo. La mandataria sostuvo que, pese a la espera, el Ejecutivo continúa avanzando en otras acciones vinculadas principalmente con la lucha contra el crimen organizado: “Nosotros seguimos avanzando más allá de lo que ellos digan”, afirmó. El Ejecutivo presentó su solicitud de facultades legislativas al Congreso para impulsar reformas en distintas materias, entre ellas seguridad ciudadana, sistema penitenciario, impuestos y legislación laboral. El pedido fue presentado luego de que el Gobierno replanteara algunos puntos incluidos inicialmente en el proyecto. Fujimori vinculó la necesidad de contar con herramientas adicionales con la lucha contra el crimen organizado y destacó los recientes compromisos internacionales asumidos por el Perú. “Esta semana que ha pasado hemos hecho que el Perú, además de ser parte del Compromiso de Santiago, hoy sea parte además del Escudo de las Américas”, señaló. El Compromiso de Santiago reúne a países de la región para fortalecer la cooperación frente al crimen organizado transnacional y el narcotráfico, mientras que el Escudo de las Américas busca reforzar la coordinación internacional frente a estas amenazas. La presidenta también reconoció el papel de las Fuerzas Armadas y la Policía Nacional en la lucha contra el terrorismo y trazó un paralelo con el actual escenario de inseguridad. “Acá reconozco y agradezco a las FF.AA. y PNP, que ayudaron a derrotar al terrorismo y permitieron que el Perú derrote a Sendero y MRTA. Hoy tenemos otro problema, que es la criminalidad organizada”, manifestó.</t>
+          <t>De acuerdo con la plataforma de inscripción habilitada por la Sunat se han registrado a la fecha 85,484 ciudadanos, de los cuales 58.5% son de Lima y 41.5% de los demás departamentos del país.
+Respecto de las dependencias lideran las listas de inscripción las regiones de Arequipa, La Libertad, Piura y Lambayeque.
+Asimismo, se han registrado casi 1.9 millones de comprobantes de pago, de los cuales más de 932,000 corresponden a Lima, más de 120,000 a Arequipa y más de 102,000 al departamento de La Libertad.
+Sorteo para Lima y provincias El Sorteo Virtual de Comprobantes de Pago tiene por objetivo promover el uso de los comprobantes electrónicos en todo el país y, en esta oportunidad, tendrá dos ediciones: la primera se realizará el 16 de octubre del 2026 y la segunda el 16 de febrero del 2027.
+En total se entregarán 416 premios distribuidos en 208 por cada edición.
+En cada sorteo se contará con dos grupos de participantes: uno para Lima y otro para provincias.
+En los sorteos podrán participar personas naturales mayores de edad, peruanas o extranjeras con sus respectivos documentos de identidad.
+Premios de los sorteos Los premios en cada edición se distribuirán de la siguiente manera: • 120 premios de S/ 500 • 70 premios de S/ 1,000 • 10 premios de S/ 5,000 • 5 premios de S/ 10,000 • 1 premio de S/ 20,000 • 1 premio de S/ 50,000 • 1 premio de S/ 100,000 Registro y requisitos Los interesados en participar deberán registrarse aquí consignando su tipo y número de documento de identidad, fecha de nacimiento, nombres y apellidos, número de celular y correo electrónico.
+Una vez inscritos, podrán consignar los datos de los comprobantes de pago electrónicos: RUC del emisor, tipo de comprobante, serie, número y fecha de emisión.
+Cada participante podrá registrar hasta tres comprobantes por cada número de RUC y por cada fecha de emisión.
+Para el sorteo del 16 de octubre del 2026 serán válidos los comprobantes emitidos entre el 1 de julio y el 30 de septiembre del 2026, los cuales sólo podrán registrarse hasta el próximo 2 de octubre del 2026.
+Más en Andina: ?? La expansión de los pagos digitales en el Perú plantea un nuevo desafío para bancos y fintechs: garantizar que sus sistemas puedan responder de forma segura a millones de operaciones simultáneas.
+?? https://t.co/0NypVjF21m ?? William Rios Rosales pic.twitter.com/SLqHQOCDjL — Agencia Andina (@Agencia_Andina) September 28, 2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/politica/gobierno/keiko-fujimori-sobre-facultades-legislativas-estamos-demostrando-paciencia-porque-llevan-semanas-ultimas-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-sunat-inicio-inscripcion-para-sorteo-comprobantes-pago-registrate-este-link-1093675.aspx</t>
         </is>
       </c>
     </row>
@@ -679,10 +702,61 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Presidenta Keiko Fujimori inspecciona la comisaría de Reque</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>El gobernador regional de Chiclayo, Jorge Pérez Flores, acompaña a la Jefa de Estado en la supervisión de la sede policial.
+Durante la visita, el cappitán PNP José Ruiz Barturén, encargado de la comisaría de Reque, guió a la mandataria Fujimori Higuchi por los ambientes del local y explicó cómo se desarrolla el trabajo en esa dependencia.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-presidenta-keiko-fujimori-inspecciona-comisaria-reque-1093584.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Keiko Fujimori sobre facultades legislativas: “Estamos demostrando paciencia porque llevan semanas”</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>La presidenta Keiko Fujimori cuestionó este domingo la demora del Congreso en el trámite de las facultades legislativas solicitadas por el Ejecutivo y aseguró que su gobierno está mostrando “paciencia” mientras espera que el Parlamento se pronuncie. “Estamos esperando facultades por parte del Congreso, estamos demostrando paciencia porque llevan semanas”, declaró Fujimori durante una actividad en la ciudad de Reque, en Lambayeque, donde participó en la inauguración del mercado modelo. La mandataria sostuvo que, pese a la espera, el Ejecutivo continúa avanzando en otras acciones vinculadas principalmente con la lucha contra el crimen organizado: “Nosotros seguimos avanzando más allá de lo que ellos digan”, afirmó. El Ejecutivo presentó su solicitud de facultades legislativas al Congreso para impulsar reformas en distintas materias, entre ellas seguridad ciudadana, sistema penitenciario, impuestos y legislación laboral. El pedido fue presentado luego de que el Gobierno replanteara algunos puntos incluidos inicialmente en el proyecto. Fujimori vinculó la necesidad de contar con herramientas adicionales con la lucha contra el crimen organizado y destacó los recientes compromisos internacionales asumidos por el Perú. “Esta semana que ha pasado hemos hecho que el Perú, además de ser parte del Compromiso de Santiago, hoy sea parte además del Escudo de las Américas”, señaló. El Compromiso de Santiago reúne a países de la región para fortalecer la cooperación frente al crimen organizado transnacional y el narcotráfico, mientras que el Escudo de las Américas busca reforzar la coordinación internacional frente a estas amenazas. La presidenta también reconoció el papel de las Fuerzas Armadas y la Policía Nacional en la lucha contra el terrorismo y trazó un paralelo con el actual escenario de inseguridad. “Acá reconozco y agradezco a las FF.AA. y PNP, que ayudaron a derrotar al terrorismo y permitieron que el Perú derrote a Sendero y MRTA. Hoy tenemos otro problema, que es la criminalidad organizada”, manifestó.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/politica/gobierno/keiko-fujimori-sobre-facultades-legislativas-estamos-demostrando-paciencia-porque-llevan-semanas-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Expoalimentaria 2026 generó expectativas de negocios por US$ 1,100 millones</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Durante la ceremonia de clausura, destacó que la decimoctava edición de la feria permitió mostrar una oferta cada vez más diversificada, con productos que incorporan transformación, innovación y mayor valor agregado, además de nuevos formatos y combinaciones orientadas a las tendencias de consumo.
 “La Expoalimentaria nos ha permitido mostrar al mundo un Perú innovador y confiable.
@@ -714,27 +788,27 @@
 ?? https://t.co/yW3Z2Q5Amh pic.twitter.com/KwH2q7gAT3 — Agencia Andina (@Agencia_Andina) September 21, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-expoalimentaria-2026-genero-expectativas-negocios-1100-millones-1093566.aspx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Recuperación del turismo e interés por viajes sostenibles abren oportunidades para el Perú</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>En el marco del Día Mundial del Turismo, el análisis del Observatorio Nacional de Prospectiva del Ceplan destaca la importancia de aprovechar estas tendencias con una planificación que articule el crecimiento del sector, la conservación del patrimonio y el bienestar de las comunidades.
 Una de las señales de recuperación se observa en los establecimientos de hospedaje.
@@ -759,27 +833,27 @@
 ?? https://t.co/yW3Z2Q5Amh pic.twitter.com/KwH2q7gAT3 — Agencia Andina (@Agencia_Andina) September 21, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-recuperacion-del-turismo-e-interes-viajes-sostenibles-abren-oportunidades-para-peru-1093569.aspx</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sector Ambiente promueve acciones para recuperar y conservar el litoral de Lambayeque</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Entre los principales avances destaca el proyecto de mejoramiento y ampliación del sistema de gestión de residuos sólidos, promovido por la Municipalidad Provincial de Chiclayo, que beneficiará directamente a más de 631 mil habitantes e incluye infraestructura para la disposición final y plantas de valorización de residuos orgánicos e inorgánicos.
 Asimismo, se concretó el cierre del botadero Pampas de Reque , una medida importante para reducir riesgos ambientales y sanitarios.
@@ -793,27 +867,27 @@
 ?? https://t.co/vJ3My16jcj pic.twitter.com/4wOlTxmfYF — Agencia Andina (@Agencia_Andina) September 27, 2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-sector-ambiente-promueve-acciones-para-recuperar-y-conservar-litoral-lambayeque-1093571.aspx</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>“La Ruta de León”: PCM recoge demandas para atender necesidades prioritarias de población</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>La reunión, que se desarrolló en el Palacio Municipal de Chiclayo, convocó a representantes del Gobierno Nacional, gobiernos regionales y municipales.
 Durante la jornada se instalaron cuatro mesas de trabajo, en las cuales las autoridades locales expusieron sus expectativas y propuestas de obras adicionales para sus provincias.
@@ -823,27 +897,27 @@
 El Grupo de Trabajo Multisectorial "La Ruta de León" , es una iniciativa estratégica que tiene como objetivo principal la ejecución de 67 intervenciones clave para el desarrollo territorial y sostenible de Piura, Lambayeque, La Libertad y Callao, regiones que formaron parte de la vida del papa León XIV durante su paso por el Perú.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-la-ruta-leon-pcm-recoge-demandas-para-atender-necesidades-prioritarias-poblacion-1093575.aspx</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Presidenta Keiko Fujimori inaugurará moderno Mercado de Abastos de Reque</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>En su décimo quinto viaje de trabajo, la jefa de Estado está acompañada del ministro de la Producción, Juan Carlos Requejo, el gobernador regional de Lambayeque, Jorge Pérez; el alcalde distrital de Reque, Manuel Neciosup; senadores y diputados de la República.
 La obra fue ejecutada a través del Programa Nacional de Diversificación Productiva (PNDP) del Ministerio de la Producción (PRODUCE).
@@ -854,27 +928,27 @@
 Para cumplir esta actividad, la presidenta de la República llegó esta mañana a la Base Aérea Teniente Coronel Pedro Ruiz Gallo de Chiclayo, donde fue recibida por autoridades castrenses.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-keiko-fujimori-inaugurara-moderno-mercado-abastos-reque-1093577.aspx</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Presidenta Fujimori: Gobierno tiene la decisión política de combatir al crimen organizado</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>“Lo más importante es la decisión política para combatir a estas lacras criminales y devolverles la paz y la tranquilidad a los peruanos” , subrayó al hacer uso de la palabra en la ceremonia de inauguración del Mercado Modelo de Reque, en la región Lambayeque.
 La jefa de Estado también resaltó su reconocimiento y agradecimiento a las integrantes de las Fuerzas Armadas y de la Policía Nacional que ayudaron a derrotar a las organizaciones terroristas de Sendero Luminoso y del MRTA.
@@ -891,60 +965,9 @@
 Pero sabemos también que el Perú va a tener retos muy difíciles en los próximos meses: el fenómeno El Niño , que ya está afectando; por eso les digo a los hermanos pescadores que el ministro (de Producción) se va a quedar acá para conversar con todos ustedes y darles el apoyo que necesitan" , expresó.</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-fujimori-gobierno-tiene-decision-politica-combatir-al-crimen-organizado-1093582.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Presidenta Keiko Fujimori inspecciona la comisaría de Reque</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>El gobernador regional de Chiclayo, Jorge Pérez Flores, acompaña a la Jefa de Estado en la supervisión de la sede policial.
-Durante la visita, el cappitán PNP José Ruiz Barturén, encargado de la comisaría de Reque, guió a la mandataria Fujimori Higuchi por los ambientes del local y explicó cómo se desarrolla el trabajo en esa dependencia.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-presidenta-keiko-fujimori-inspecciona-comisaria-reque-1093584.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Presidenta Fujimori inspeccionó Centro de Salud de Reque</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>La mandataria recorrió las instalaciones del Centro de Salud y fue informada de los servicios que brinda a la población.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-inspecciono-centro-salud-reque-1093588.aspx</t>
         </is>
       </c>
     </row>
@@ -990,10 +1013,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Presidenta Fujimori inspeccionó Centro de Salud de Reque</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>La mandataria recorrió las instalaciones del Centro de Salud y fue informada de los servicios que brinda a la población.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-inspecciono-centro-salud-reque-1093588.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Presidenta: “Esperamos las facultades legislativas, pero nosotros seguimos avanzando"</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>“Estamos esperando facultades de parte del Congreso .
 Estamos demostrando paciencia porque llevan semanas.
@@ -1029,27 +1077,27 @@
 Gracias por llegar a nuestro distrito, compartir este momento con nuestros comerciantes y ser parte de esta jornada que quedará en la memoria de nuestra población”, expresó.</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-esperamos-las-facultades-legislativas-pero-nosotros-seguimos-avanzando-1093600.aspx</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>ERM 2026: JNE fiscaliza simulacro de sistema de cómputo y capacitación a miembros de mesa</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>La finalidad fue comprobar la funcionalidad del software electoral para el correcto procesamiento de las actas electorales y la seguridad de los mecanismos de transmisión de los datos.
 La labor se desarrolló en el centro de cómputo de la sede principal de la Oficina Nacional de Procesos Electorales (ONPE) en Lima y en las Oficinas Descentralizadas de Procesos Electorales (ODPE) en las diversas regiones del país.
@@ -1060,27 +1108,27 @@
 Lee también: [ ERM 2026: Sistema de Cómputo Electoral de la ONPE demuestra funcionalidad y exactitud ] "El propósito de la labor fiscalizadora del JNE es verificar que el personal de la ONPE imparta adecuadamente los lineamientos establecidos con la finalidad que los miembros de mesa comprendan adecuadamente el importante rol que les toca cumplir el domingo 4 de octubre, de forma que se pueda asegurar la correcta marcha de la jornada electoral", informó el organismo electoral.</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-erm-2026-jne-fiscaliza-simulacro-sistema-computo-y-capacitacion-a-miembros-mesa-1093617.aspx</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Presidenta supervisó avances en la construcción de tramo norte de la Autopista del Sol</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>“Estamos en los últimos trámites.
 Hemos venido despachando con el ministro de Transportes para inaugurar la obra en las próximas semanas ”, manifestó desde la mencionada obra.
@@ -1100,27 +1148,27 @@
 Una vez puesto en funcionamiento, el nuevo Centro de Salud de Reque beneficiará a más de 26 mil habitantes del distrito y zonas aledañas, quienes contarán con nuevos ambientes, equipamiento y servicios para su atención.</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-superviso-avances-la-construccion-tramo-norte-de-autopista-del-sol-1093625.aspx</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46292</v>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Congreso: Comisión de Ética se reúne mañana para ver denuncias contra tres diputados</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>De acuerdo a la agenda de la cuarta sesión ordinaria de la comisión presidida por el diputado, Henry Albañil Carmona (Obras), la sesión se realizará en la sala Fabiola Salazar Leguía, ubicada en el edificio Víctor Raúl Haya de la Torre.
 En primer término, se verá la denuncia de oficio por la presunta vulneración de la ética parlamentaria contra el diputado Julián Luis Pérez Mallqui, contra quien se aprobó un informe de calificación que recomienda investigarlo por la presunta agresión a su expareja.
@@ -1129,44 +1177,9 @@
 Asimismo, en la agenda se indica que se verá el informe de calificación en el Expediente 004-2026-2027/CEP-CD, contra la diputada Milagros Karina Santana Vera (PBG), en relación a un incidente registrado en la ciudad de Huaral.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-congreso-comision-etica-se-reune-manana-para-ver-denuncias-contra-tres-diputados-1093632.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46291</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ANA supera el 50 % de avance en limpieza y descolmatación de los ríos La Leche y Reque</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>En el río La Leche, sector Manchuria, los trabajos alcanzan un avance de 63,33 %, equivalente a 1,90 kilómetros de los 3,00 kilómetros programados.
-La intervención comprende labores de limpieza y descolmatación, así como la conformación de bordos con material propio, con la finalidad de mejorar las condiciones hidráulicas del sector intervenido y contribuir a reducir su exposición ante eventuales incrementos de caudal.
-En tanto, en el río Reque, sector Comunidad Campesina San Pedro, se registra un avance de 83,59 %, correspondiente a 1,35 kilómetros de los 1,615 kilómetros programados.
-En este tramo se ejecutan trabajos de limpieza y descolmatación, además de la construcción de un dique enrocado en ambas márgenes del río.
-El director de la Autoridad Administrativa del Agua Jequetepeque Zarumilla informó que las actividades se desarrollan en doble turno, con el despliegue de maquinaria y equipos de las Administraciones Locales de Agua Motupe Olmos La Leche y Chancay Lambayeque, a fin de mantener el ritmo de las intervenciones programadas.
-Para los trabajos en el río La Leche se dispone de 4 tractores, 3 excavadoras, 2 cargadores frontales, 2 volquetes, 1 camioneta y 2 luminarias.
-En el río Reque se cuenta con 2 excavadoras, 3 tractores, 2 luminarias y 1 camioneta, equipos destinados a las labores previstas en ambos sectores.
-Las intervenciones se ejecutan en el marco del Decreto de Urgencia N.° 008-2026, que establece medidas extraordinarias para la ejecución de intervenciones ante peligro inminente por intensas precipitaciones pluviales asociadas al fenómeno El Niño 2026-2027.
-De acuerdo con la planificación de estas intervenciones, los trabajos están orientados a reducir los riesgos asociados a posibles eventos hidrometeorológicos y contribuir a la protección de la población, áreas agrícolas e infraestructura ubicada en sectores vulnerables.
-En conjunto, las acciones comprenden aproximadamente 250 familias y 242 hectáreas de cultivos, según la información técnica proporcionada para estas intervenciones.
-La ANA continuará realizando el seguimiento técnico de los trabajos programados, en coordinación con las instancias competentes, contribuyendo a fortalecer las acciones de prevención y reducción del riesgo de desastres vinculadas con los recursos hídricos en la región Lambayeque.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-ana-supera-50-avance-limpieza-y-descolmatacion-los-rios-leche-y-reque-1093511.aspx</t>
         </is>
       </c>
     </row>
@@ -1177,26 +1190,40 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ERM 2026: ODPE Lambayeque recibe material electoral para comicios del 4 de octubre</t>
+          <t>Presidenta anuncia que recibió invitación de Nayib Bukele para visitar El Salvador</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El vehículo que transportó los insumos electorales llegó a la sede de la oficina descentralizada el pasado miércoles 23 de septiembre, resguardado por un comisionado de la ONPE, personal de la Policía Nacional del Perú y mediante un sistema de monitoreo satelital, garantizando así su integridad durante todo el trayecto.
-La recepción del material y su traslado al almacén electoral se realizó en presencia del jefe de la ODPE Lambayeque, Ethel Moreno García; y representantes del Jurado Especial Electoral (JEE) de Chiclayo, quienes dieron conformidad a los precintos de seguridad del vehículo de carga pesada que lo trasladó hasta la sede de la oficina descentralizada.
-El material electoral está conformado por tres paquetes; cajas de sufragio (con padrón electoral, lista de electores, actas electorales, cédulas de sufragio, manual para miembros de mesa, sobres plásticos para la remisión de actas, láminas para la protección de resultados y sobres para la impugnación del voto), paquetes con señales y rótulos para los locales de votación, ánforas y cabinas de votación; y útiles de escritorio (lapiceros, cintas adhesivas, tampones para la impresión de la huella dactilar).
-En estricto cumplimiento del cronograma electoral, cada oficina descentralizada distribuirá el material a sus respectivos locales de votación en una segunda fase programada para los próximos días.
-En el ámbito de la ODPE Lambayeque se instalarán 1,201 mesas de sufragio en 170 locales de votación, distribuidos en 18 distritos y 50 centros poblados de toda la provincia, donde se espera que acudan a las urnas más de 350 371 electores hábiles.
-La ODPE Lambayeque exhorta a la ciudadanía a informarse únicamente a través de los canales oficiales de la ONPE y a verificar con anticipación su local de votación, a fin de acudir a la jornada electoral con la debida previsión.</t>
+          <t>Así lo señaló durante una transmisión en vivo en sus redes sociales, en la cual también participó el canciller Carlos Espá , quien confirmó la noticia.
+La jefa de Estado calificó este anuncio como "una gran noticia" e indicó que por el momento no podía dar más detalles de la invitación que le ha extendido el mandatario salvadoreño.
+Por su parte, el ministro de Relaciones Exteriores, expresó su emoción y resaltó que el presidente Bukele "tiene muchas lecciones aprendidas para compartir" con nuestro país.
+"Estoy seguro que esas lecciones aprendidas también van a servir para que nosotros podamos responder efectivamente a las justas demandas del pueblo peruano por mayor seguridad ciudadana ", agregó Espá y Garcés Alvear.
+Lee también: [ Presidenta: “Esperamos las facultades legislativas, pero nosotros seguimos avanzando" ] Invitación a la reina Máxima En otro momento, mientras hacía un recuento de sus actividades en Nueva York, a donde viajó con el canciller y otros tres ministros para participar en el periodo de sesiones de la Asamblea de las Naciones Unidas, mencionó su reunión con la reina Máxima de los Países Bajos, a quien invitó a visitar nuestro país.
+Precisó que la reina consorte —nacida en Argentina— dirige en la ONU un programa que promueve la inclusión financiera de las mujeres y que el Perú está adscrito a esta iniciativa.
+"Fue un gusto poder saludarla y también ratificarle el compromiso de nuestro país para poder, a través de los programas de microcrédito, ayudar a diferentes mujeres emprendedoras.
+Esto nos permite luego que estas mamás puedan darle mejor calidad de vida a sus hijos, a disminuir las cifras de pobreza, así que hemos invitado a la reina Máxima para que el próximo año ella pueda venir a nuestro país " , indicó la jefa de Estado.
+Interés de inversionistas En otro momento de la transmisión, la presidenta Fujimori resaltó que en diferentes actividades en las que participó durante su viaje a Estados Unidos pudo hablar del Perú y de sus auspiciosas cifras macroeconómicas, lo que ha generado el interés de inversionistas.
+"Les hemos hablado del Banco Central de Reserva, de la Constitución Política de nuestro país, de las reglas claras.
+Así que yo creo que han sido muy buenas reuniones ", indicó.
+Destacó también la importancia de las micro y pequeñas empresas para mover la economía del Perú.
+En esa línea, resaltó que su Gobierno los ayudará a evitar trabas burocráticas que puedan frenar su dinamismo.
+Relanzamiento de Alianza del Pacífico Por su parte, el canciller Espá mencionó que, en el marco del viaje a Nueva York, sostuvo diferentes reuniones bilaterales y entre ellas destacó el encuentro con su homólogo de México, Roberto Velazco , en donde se abordó la transmisión de la presidencia pro tempore de la Alianza del Pacífico al Perú el próximo año.
+" Va a ser el relanzamiento de la Alianza del Pacífico, que lo que busca es no solamente la integración comercial y económica, sino la integración financiera de las bolsas de valores de los países que integran la Alianza del Pacífico.
+Va a ser muy importante y veo con mucho optimismo, esperanza también, lo fructífera que va a ser su encuentro con la presidenta (Claudia) Sheinbaum de México ", expresó a la jefa de Estado.
+Relación con Venezuela y Marruecos El titular de Relaciones Exteriores resaltó también su reunión con el canciller de Venezuela, Félix Plasencia , tras haberse normalizado las relaciones del Perú con dicho país a nivel consular, en beneficio de los connacionales que se encuentran allá.
+Indicó, además, que el Perú ve con mucha atención la evolución de su situación política e hizo votos para el restablecimiento de la democracia en Venezuela.
+"En esa medida, por supuesto, nosotros vamos a ser de los primeros países que vamos a establecer relaciones diplomáticas (con Venezuela) " , sostuvo Espá.
+De igual modo, destacó la reunión bilateral con su homólogo de Marruecos, Nasser Bourita, con quien emitió un comunicado conjunto en donde el Perú respalda su posición sobre el Sahara Occidental y se relanzan las relaciones comerciales con el país africano, lo que consideró muy auspicioso.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-erm-2026-odpe-lambayeque-recibe-material-electoral-para-comicios-del-4-octubre-1093510.aspx</t>
+          <t>https://andina.pe/agencia/noticia-presidenta-anuncia-recibio-invitacion-nayib-bukele-para-visitar-salvador-1093633.aspx</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1234,30 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ERM 2026: JNE reporta 83 casos de amenazas, extorsiones y ataques a candidatos</t>
+          <t>Produce acelera acciones para reactivar la pesca artesanal en San José, Lambayeque</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>En entrevista con la Agencia Andina , Eugenia Fernán Zegarra Miranda , directora Nacional de Estudios, Estrategias y Coordinación Territorial del JNE informó que estas amenazas corresponden al periodo de las ERM 2026 hasta el 25 de setiembre.
-Lea también: ERM 2026: Conoce aquí si eres miembro de mesa para los comicios regionales y municipales “Son 83 casos que hemos podido reportar y tienen que ver con 21 regiones.
-Las regiones que mayormente registran los casos son Lima, La Libertad, Áncash, Cajamarca y Junín .
-Y esto coincide con el mapa de alta conflictividad en algunas regiones” , indicó.
-De acuerdo a las cifras del JNE las cifras de amenazas, extorsiones y ataques en regiones son: Lima (21); La Libertad (16), Áncash (7), Cajamarca (5), Junín (7), Piura (4), Ica (3), Callao (3), Ayacucho (3), San martín (2), Huánuco (2), Huancavelica (1), Moquegua (1), Puno (1), Tumbes (1), Lambayeque (1), Ucayali (1), Apurímac (1), Arequipa (1) y Amazonas (1).
-Fernán Zegarra Miranda expresó que desde el JNE se condena la violencia venga de donde venga, especialmente agravada en la actual contienda electoral de ERM 2026 .
-Lea también: ERM 2026: Conoce tu local de votación para las elecciones del 4 de octubre “Lamentablemente, estos ataques se están incrementando día a día, de tal suerte que ha habido en nueve días alrededor de 23 acciones que tienen que ver con amenazas, extorsiones y ataques directos en esta contienda electoral” , expresó.
-Crimen de Susy Aponte La funcionaria del JNE indicó que dentro de las indagaciones del organismo electoral se encuentra el crimen de la periodista y candidata a gobernadora regional de Áncash por el movimiento Socios por Áncash, Susy Isabel Aponte Polo, conocida como "La China Polo" .
-“Estamos haciendo seguimiento y monitoreo de la atención que se le está dando en la investigación que se está siguiendo ya en la Fiscalía y esto va en avance porque nos interesa también que estos hechos no queden impunes.
-Preocupados también porque esto ha sido en un acto público y a la luz del día, las condiciones han sido realmente preocupantes” , dijo.
-Lea también: JNE expresa condena enérgica ante homicidio de candidata a Gobierno Regional de Áncash Pautas y recomendaciones Fernán Zegarra Miranda señaló que el JNE ha considerado importante difundir una serie de orientaciones para que la campaña electoral, especialmente los cierres de campañas electorales (el 1 de octubre hasta las 23.59 horas), se lleven a cabo con la mayor seguridad para los actores políticos , teniendo en cuenta que son aproximadamente 97 mil candidatos a nivel nacional.
-“Sí preocupa porque en realidad estos actos de carácter público, aun en ambientes cerrados, concurren varias personas; debieran prestarse con las garantías del caso.
-Por eso el Jurado Nacional de Elecciones, en su página web, está publicando y se ha precisado algunas pautas para solicitar las garantías de orden público en concentraciones de índole político ” , sostuvo.
-La funcionaria del JNE precisó que entre las pautas se explica que las garantías tienen que ser solicitadas por el representante legal o personero legal de cada organización política, que deben ser presentadas, por ejemplo, en el caso de Lima Metropolitana y el Callao ante la Dirección General de Gobierno del Interior, y en provincias ante las prefecturas y subprefecturas.
-Lea también: ONPE: miembros de mesa tendrán más de cuatro mil locales para entrenarse este domingo “¿Por qué interesa utilizar este mecanismo legal? Porque haciendo esta solicitud, que tiene valor de declaración jurada, lo que se logra es que la Policía Nacional pueda prestar las garantías de orden público que se necesitan para las presentaciones que darán los candidatos en lugares abiertos al público” , manifestó.
-Zegarra Miranda confirmó que el JNE se ha enviado también a cada organización política, a través de su personero o representante legal, el citado manual para garantizar la seguridad de los actores políticos .
-Además, aseguró que se les proporcionó pautas para solicitar las garantías .</t>
+          <t>El titular de la cartera explicó que las decisiones sobre el manejo pesquero requieren el respaldo científico del Instituto del Mar del Perú (Imarpe) , por lo que destacó el fortalecimiento de su equipo científico y el trabajo que se realiza para contar con información actualizada sobre las condiciones del mar y los recursos disponibles.
+“Yo no he venido acá a quejarme, he venido a ser parte de la solución, junto con ustedes.
+El sistema de cuotas (de pesca) es una herramienta, pero por sí sola no es suficiente.
+Lo que tenga que decidirse, tiene que decidirse ya.
+No puede esperar”, señaló Requejo.
+Lee también: [ Presidenta anuncia que recibió invitación de Nayib Bukele para visitar El Salvador ] En ese marco, informó que se encuentra en desarrollo un crucero de investigación en el que participa parte de la flota, el cual permitirá obtener información sobre especies como anchoveta, bonito y calamar.
+Agregó que se busca contar con los resultados lo antes posible, a fin de evaluar nuevas medidas.
+Finalmente, Requejo reafirmó su compromiso de trabajar junto a los pescadores para encontrar alternativas que permitan mantener la actividad hasta fin de año y avanzar hacia un escenario de mayor ordenamiento para el próximo periodo.
+"Esta visita se dio en cumplimiento del compromiso de la presidenta de la República, Keiko Fujimori, y de la política del Gobierno de trabajar directamente en los territorios, escuchando las necesidades de los sectores productivos y buscando soluciones directamente con los actores", destacó Produce.
+Posteriormente, el ministro participó en la inauguración del Gran Mercado de Abastos junto con la mandataria, tras lo cual continuó con el trabajo territorial y el diálogo directo con el sector para abordar la agenda pendiente de la pesca artesanal.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-erm-2026-jne-reporta-83-casos-amenazas-extorsiones-y-ataques-a-candidatos-1093505.aspx</t>
+          <t>https://andina.pe/agencia/noticia-produce-acelera-acciones-para-reactivar-pesca-artesanal-san-jose-lambayeque-1093635.aspx</t>
         </is>
       </c>
     </row>
